--- a/DataTables/Datas/bag.xlsx
+++ b/DataTables/Datas/bag.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>ownerid</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>##备注</t>
         </is>
       </c>
     </row>
